--- a/outputs/evaluation/architecture/validation/CF_M09/run_1/CF_M09_arch_eval_gt_report.xlsx
+++ b/outputs/evaluation/architecture/validation/CF_M09/run_1/CF_M09_arch_eval_gt_report.xlsx
@@ -507,21 +507,21 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>P_06</t>
+          <t>P_04</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Provider</t>
+          <t>Observer</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Allows sharing information between React components without using props.</t>
+          <t>The observer pattern is a software design pattern that defines a one-to-many dependency between objects, so that when one object changes its state, all objects that depend on it are notified and updated automatically.</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.6886</v>
+        <v>0.6791</v>
       </c>
     </row>
     <row r="3">
@@ -577,62 +577,62 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CF_M09_AU07</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
+          <t>CF_M09_AU11</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>On one side is the client, who makes the various requests, and on the other side is the server, who receives and processes them.</t>
+          <t>This is the part responsible for displaying information to the user.</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CF_M09_AU06, CF_M09_AU05</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>client, waapiti platform</t>
-        </is>
-      </c>
+          <t>CF_M09_P03</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>P_01</t>
+          <t>P_04</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Client-Server</t>
+          <t>Observer</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>The platform is a web service that follows the client-server architecture.</t>
+          <t>The observer pattern is a software design pattern that defines a one-to-many dependency between objects, so that when one object changes its state, all objects that depend on it are notified and updated automatically.</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.8557</v>
+        <v>0.7618</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CF_M09_AU11</t>
+          <t>CF_M09_AU12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>Actions</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>This is the part responsible for displaying information to the user.</t>
+          <t>These are the actions that the user can perform.</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -657,32 +657,32 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>P_05</t>
+          <t>AU_08</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Observer</t>
+          <t>React</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Defines a one-to-many dependency between objects so that when one object changes state, all its dependents are notified.</t>
+          <t>JavaScript library used to build user interfaces.</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.7618</v>
+        <v>0.7452</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CF_M09_AU12</t>
+          <t>CF_M09_AU13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Actions</t>
+          <t>Dispatcher</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>These are the actions that the user can perform.</t>
+          <t xml:space="preserve"> It is responsible for receiving the actions and sending them to the store to modify its state.</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -707,32 +707,32 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>AU_08</t>
+          <t>AU_02</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>React</t>
+          <t>Server</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>JavaScript library used for building user interfaces in the frontend.</t>
+          <t>The server is the software that is responsible for processing user requests.</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.7452</v>
+        <v>0.6807</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CF_M09_AU13</t>
+          <t>CF_M09_AU14</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dispatcher</t>
+          <t>Store</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> It is responsible for receiving the actions and sending them to the store to modify its state.</t>
+          <t>It is responsible for storing the application state.</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -757,42 +757,38 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>P_06</t>
+          <t>AU_06</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Provider</t>
+          <t>Business Service</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Allows sharing information between React components without using props.</t>
+          <t>Service responsible for the management, authentication and authorization of platform users.</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.7081</v>
+        <v>0.6739000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CF_M09_AU14</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Store</t>
-        </is>
-      </c>
+          <t>CF_M09_AU15</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>It is responsible for storing the application state.</t>
+          <t>They are defined as JavaScript objects and indicate the intention to modify the application's state.</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -800,34 +796,38 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CF_M09_P03</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>CF_M09_AU12, CF_M09_AU14</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>actions, store</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>P_06</t>
+          <t>AU_09</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Provider</t>
+          <t>NestJS</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Allows sharing information between React components without using props.</t>
+          <t>Framework for building backend applications.</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.6902</v>
+        <v>0.6073</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CF_M09_AU15</t>
+          <t>CF_M09_AU16</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -838,7 +838,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>They are defined as JavaScript objects and indicate the intention to modify the application's state.</t>
+          <t>It is responsible for receiving the actions and sending them to the store to modify its state.</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -846,49 +846,49 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CF_M09_AU12, CF_M09_AU14</t>
+          <t>CF_M09_AU13, CF_M09_AU14</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>actions, store</t>
+          <t>dispatcher, store</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>P_07</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Module</t>
-        </is>
-      </c>
+          <t>AU_18</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Allows encapsulating information and exposing only what is intended to be shared.</t>
+          <t>This is the service that performs all the important logic of the platform. It is the service that has communication with the data layer.</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.6199</v>
+        <v>0.712</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CF_M09_AU16</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
+          <t>CF_M09_AU17</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Redux</t>
+        </is>
+      </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>It is responsible for receiving the actions and sending them to the store to modify its state.</t>
+          <t>Redux is a JavaScript library that allows you to implement the Flux architecture.</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -896,149 +896,149 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CF_M09_AU13, CF_M09_AU14</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>dispatcher, store</t>
-        </is>
-      </c>
+          <t>CF_M09_P03</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>AU_18</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
+          <t>AU_08</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>React</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Es el servicio que tiene comunicaci´ on con la capa de datos.</t>
+          <t>JavaScript library used to build user interfaces.</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.6985</v>
+        <v>0.7194</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CF_M09_AU17</t>
+          <t>CF_M09_AU18</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Redux</t>
+          <t>Presentation layer (Backend)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Redux is a JavaScript library that allows you to implement the Flux architecture.</t>
+          <t>In this case, the presentation layer is not complex. It corresponds to the user's web browser.</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CF_M09_P03</t>
+          <t>CF_M09_P02</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>AU_08</t>
+          <t>AU_03</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>React</t>
+          <t>Presentation Layer</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>JavaScript library used for building user interfaces in the frontend.</t>
+          <t>It is the layer that is responsible for displaying information to the user.</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0.7194</v>
+        <v>0.9188</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CF_M09_AU18</t>
+          <t>CF_M09_AU22</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Presentation layer (Backend)</t>
+          <t>REST</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>In this case, the presentation layer is not complex. It corresponds to the user's web browser.</t>
+          <t>Defines REST API routes and processes requests to send them to the functional service.</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CF_M09_P02</t>
+          <t>CF_M09_AU20</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>AU_03</t>
+          <t>AU_14</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Presentation Layer</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>It is the layer that is responsible for displaying information to the user.</t>
+          <t>Communication protocol used between client and server.</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0.9188</v>
+        <v>0.6758999999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CF_M09_AU22</t>
+          <t>CF_M09_AU23</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>REST</t>
+          <t>RDS</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Defines REST API routes and processes requests to send them to the functional service.</t>
+          <t>RDS is a distributed relational database service. In the case of Waapiti, a MySQL database is used and contains all the system information.</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1046,49 +1046,49 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CF_M09_AU20</t>
+          <t>CF_M09_AU39</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>AU_14</t>
+          <t>AU_02</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>HTTP</t>
+          <t>Server</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Communication protocol used between client and server.</t>
+          <t>The server is the software that is responsible for processing user requests.</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0.6758999999999999</v>
+        <v>0.6213</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CF_M09_AU23</t>
+          <t>CF_M09_AU26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>RDS</t>
+          <t>User Cache</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>RDS is a distributed relational database service. In the case of Waapiti, a MySQL database is used and contains all the system information.</t>
+          <t>To improve system response speed, there is a user cache system stored in Amazon DynamoDB</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1103,78 +1103,78 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>P_06</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Provider</t>
-        </is>
-      </c>
+          <t>AU_19</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Allows sharing information between React components without using props.</t>
+          <t>For better response speed of the system, there is a user cache system stored in Amazon DynamoDB, to which the business service has access.</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0.6294999999999999</v>
+        <v>0.7637</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>CF_M09_AU28</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Typescript</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>is a superset of JavaScript. It has been used to develop both the backend.</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>60</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>CF_M09_AU26</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>User Cache</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Component</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>To improve system response speed, there is a user cache system stored in Amazon DynamoDB</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>58</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>CF_M09_AU39</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>AU_19</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
+          <t>AU_09</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>NestJS</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Cache de usuarios: Para mejorar la velocidad de respuesta del sistema, existe un sistema de cach´ e de usuarios almacenada en Amazon DynamoDB, a la cu´ al tiene acceso el servicio business.</t>
+          <t>Framework for building backend applications.</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0.7848000000000001</v>
+        <v>0.697</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CF_M09_AU28</t>
+          <t>CF_M09_AU29</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Typescript</t>
+          <t>TypeORM</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>is a superset of JavaScript. It has been used to develop both the backend.</t>
+          <t>is an ORM (Object Relational Mapping) [41] for TypeScript and JavaScript.</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -1192,39 +1192,39 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CF_M09_AU26</t>
+          <t>CF_M09_AU33</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>AU_09</t>
+          <t>AU_11</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>NestJS</t>
+          <t>MySQL</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Framework for building backend applications.</t>
+          <t>Relational database management system used in RDS.</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0.697</v>
+        <v>0.6622</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CF_M09_AU29</t>
+          <t>CF_M09_AU30</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>TypeORM</t>
+          <t>Material UI</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1234,47 +1234,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>is an ORM (Object Relational Mapping) [41] for TypeScript and JavaScript.</t>
+          <t>is a React library that contains user interface components.</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CF_M09_AU33</t>
+          <t>CF_M09_AU01</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>AU_11</t>
+          <t>AU_03</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>MySQL</t>
+          <t>Presentation Layer</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Relational database management system used for storing system information.</t>
+          <t>It is the layer that is responsible for displaying information to the user.</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0.6622</v>
+        <v>0.6683</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CF_M09_AU30</t>
+          <t>CF_M09_AU31</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Material UI</t>
+          <t>NextJS</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>is a React library that contains user interface components.</t>
+          <t>is a React meta-framework that allows you to easily create web applications (since it provides utilities such as web routing).</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -1299,32 +1299,32 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>AU_03</t>
+          <t>AU_09</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Presentation Layer</t>
+          <t>NestJS</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>It is the layer that is responsible for displaying information to the user.</t>
+          <t>Framework for building backend applications.</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0.6683</v>
+        <v>0.7692</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CF_M09_AU31</t>
+          <t>CF_M09_AU32</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NextJS</t>
+          <t>Shadcn</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>is a React meta-framework that allows you to easily create web applications (since it provides utilities such as web routing).</t>
+          <t>is a reusable UI component project that features a modern design and focuses on accessibility and ease of customization of components.</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -1342,89 +1342,89 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CF_M09_AU01</t>
+          <t>CF_M09_AU34</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>AU_09</t>
+          <t>AU_15</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>NestJS</t>
+          <t>TCP</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Framework for building backend applications.</t>
+          <t>Communication protocol used between business and functional services.</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0.7692</v>
+        <v>0.6069</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CF_M09_AU32</t>
+          <t>CF_M09_AU33</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Shadcn</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>is a reusable UI component project that features a modern design and focuses on accessibility and ease of customization of components.</t>
+          <t>It should be clear that in this project the author has worked on the entire system, both backend and frontend.</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CF_M09_AU34</t>
+          <t>CF_M09_P01</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>P_06</t>
+          <t>AU_04</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Provider</t>
+          <t>Business Layer</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Allows sharing information between React components without using props.</t>
+          <t>This layer is the core of the application and is responsible for processing all the information.</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0.6219</v>
+        <v>0.706</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CF_M09_AU33</t>
+          <t>CF_M09_AU34</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1449,82 +1449,82 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>AU_04</t>
+          <t>AU_03</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Business Layer</t>
+          <t>Presentation Layer</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>This layer is the core of the application and is responsible for processing all the information.</t>
+          <t>It is the layer that is responsible for displaying information to the user.</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0.706</v>
+        <v>0.7635</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CF_M09_AU34</t>
+          <t>CF_M09_AU35</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Modules</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>It should be clear that in this project the author has worked on the entire system, both backend and frontend.</t>
+          <t>Modules are classes that allow NestJS to organize the application.</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CF_M09_P01</t>
+          <t>CF_M09_AU02</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>AU_03</t>
+          <t>AU_04</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Presentation Layer</t>
+          <t>Business Layer</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>It is the layer that is responsible for displaying information to the user.</t>
+          <t>This layer is the core of the application and is responsible for processing all the information.</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0.7635</v>
+        <v>0.6216</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CF_M09_AU35</t>
+          <t>CF_M09_AU36</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Modules</t>
+          <t>Controllers</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Modules are classes that allow NestJS to organize the application.</t>
+          <t>Controllers are responsible for receiving and processing HTTP requests.</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -1549,32 +1549,32 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>P_07</t>
+          <t>P_01</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Module</t>
+          <t>Client-Server</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Allows encapsulating information and exposing only what is intended to be shared.</t>
+          <t>The platform is a web service that follows the client-server architecture, where the client makes requests to a server that processes them and returns the response.</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0.9649</v>
+        <v>0.6403</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CF_M09_AU36</t>
+          <t>CF_M09_AU37</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Controllers</t>
+          <t>Providers</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1584,11 +1584,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Controllers are responsible for receiving and processing HTTP requests.</t>
+          <t>Providers are classes that can act as services, repositories, factories, helpers, etc.</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1599,224 +1599,224 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>P_04</t>
+          <t>AU_06</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>MVC</t>
+          <t>Business Service</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Model-View-Controller design pattern.</t>
+          <t>Service responsible for the management, authentication and authorization of platform users.</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0.7063</v>
+        <v>0.711</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CF_M09_AU37</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Providers</t>
-        </is>
-      </c>
+          <t>CF_M09_AU38</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Providers are classes that can act as services, repositories, factories, helpers, etc.</t>
+          <t>Therefore, controllers are responsible for receiving HTTP requests and forwarding them to the providers.</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CF_M09_AU02</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
+          <t>CF_M09_AU06, CF_M09_AU19</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>client, business layer (backend)</t>
+        </is>
+      </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>P_06</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>Provider</t>
-        </is>
-      </c>
+          <t>AU_16</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Allows sharing information between React components without using props.</t>
+          <t>The client is the user of the platform. [...] The server is the software that is responsible for processing user requests. [...] The communication between both is performed through the internet using the REST API model and the HTTP communication protocol.</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0.9526</v>
+        <v>0.7089</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CF_M09_AU38</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
+          <t>CF_M09_AU39</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Data Layer (Backend)</t>
+        </is>
+      </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Therefore, controllers are responsible for receiving HTTP requests and forwarding them to the providers.</t>
+          <t>The data layer is divided into several AWS services that allow for improved system performance and scalability.</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CF_M09_AU06, CF_M09_AU19</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>client, business layer (backend)</t>
-        </is>
-      </c>
+          <t>CF_M09_P02</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>AU_17</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
+          <t>AU_05</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Data Layer</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Estas peticiones son procesadas y enviadas mediante una conexi´ on interna al servicio functional, que es el que contiene la informaci´ on sensible del sistema. La comunicaci´ on se realiza mediante el protocolo de comunicaci´ on TCP.</t>
+          <t>It is the layer that is responsible for storing all the data.</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0.707</v>
+        <v>0.9248</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CF_M09_AU39</t>
+          <t>CF_M09_P05</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Data Layer (Backend)</t>
+          <t>Provider pattern</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>The data layer is divided into several AWS services that allow for improved system performance and scalability.</t>
+          <t>The provider pattern is a software design pattern that allows sharing information between React components without the need to use props.</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CF_M09_P02</t>
+          <t>CF_M09_AU01</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>AU_05</t>
+          <t>AU_07</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Data Layer</t>
+          <t>Functional Service</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>It is the layer that is responsible for storing all the data.</t>
+          <t>This is the service that performs all the important logic of the platform.</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0.9248</v>
+        <v>0.717</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CF_M09_P02</t>
+          <t>CF_M09_P06</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Three Layers</t>
+          <t>Module Pattern</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>To decouple the components of the client-server model, a three-tier architecture has been used.</t>
+          <t>This is the most important pattern in the JavaScript language.</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>P_02</t>
+          <t>AU_04</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>3-Layer Architecture</t>
+          <t>Business Layer</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>This architecture divides the system into three parts: the presentation layer, the business layer, and the data layer.</t>
+          <t>This layer is the core of the application and is responsible for processing all the information.</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0.8511</v>
+        <v>0.6344</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CF_M09_P06</t>
+          <t>CF_M09_P07</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Module Pattern</t>
+          <t>Hook pattern</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1826,32 +1826,36 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>This is the most important pattern in the JavaScript language.</t>
+          <t>Hooks are a new feature in React that allows you to use state and other React features without writing a class.</t>
         </is>
       </c>
       <c r="E29" t="n">
         <v>59</v>
       </c>
-      <c r="F29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>CF_M09_AU01</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>P_07</t>
+          <t>AU_14</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Module</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Allows encapsulating information and exposing only what is intended to be shared.</t>
+          <t>Communication protocol used between client and server.</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0.9157999999999999</v>
+        <v>0.6038</v>
       </c>
     </row>
     <row r="30">
@@ -1893,7 +1897,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Relational database management system used for storing system information.</t>
+          <t>Relational database management system used in RDS.</t>
         </is>
       </c>
       <c r="L30" t="n">
